--- a/Impact modelling/Runs_energy_municipalities_months.xlsx
+++ b/Impact modelling/Runs_energy_municipalities_months.xlsx
@@ -474,7 +474,7 @@
         <v>0.49</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -500,16 +500,16 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -532,7 +532,7 @@
         <v>0.47</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -561,7 +561,7 @@
         <v>0.44</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -587,21 +587,21 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -616,21 +616,21 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
       </c>
       <c r="K7">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
@@ -648,7 +648,7 @@
         <v>0.42</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -677,18 +677,18 @@
         <v>0.55</v>
       </c>
       <c r="I9">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
@@ -702,22 +702,16 @@
       <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="H10">
-        <v>0.43</v>
-      </c>
       <c r="I10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
       </c>
-      <c r="K10">
-        <v>0.43</v>
-      </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -740,7 +734,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>10</v>
@@ -758,7 +752,7 @@
         <v>0.51</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -769,7 +763,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
@@ -784,21 +778,21 @@
         <v>14</v>
       </c>
       <c r="H13">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>10</v>
@@ -813,21 +807,21 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="1">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
@@ -842,10 +836,10 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="I15">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
@@ -856,7 +850,7 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="1">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
@@ -874,7 +868,7 @@
         <v>0.54</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
@@ -885,7 +879,7 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -900,21 +894,21 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="1">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -929,21 +923,21 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="I18">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="1">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -958,21 +952,21 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I19">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="1">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -987,21 +981,21 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="I20">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
       <c r="K20">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="1">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -1024,7 +1018,7 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>10</v>
@@ -1042,7 +1036,7 @@
         <v>0.53</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -1053,7 +1047,7 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -1071,18 +1065,18 @@
         <v>0.51</v>
       </c>
       <c r="I23">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
       <c r="K23">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>10</v>
@@ -1097,21 +1091,21 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>10</v>
@@ -1126,10 +1120,10 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I25">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -1140,7 +1134,7 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -1158,18 +1152,18 @@
         <v>0.55</v>
       </c>
       <c r="I26">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
       <c r="K26">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -1192,7 +1186,7 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -1207,10 +1201,10 @@
         <v>14</v>
       </c>
       <c r="H28">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I28">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
@@ -1221,7 +1215,7 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>10</v>
@@ -1239,7 +1233,7 @@
         <v>0.59</v>
       </c>
       <c r="I29">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
@@ -1250,7 +1244,7 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>10</v>
@@ -1268,7 +1262,7 @@
         <v>0.63</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -1279,7 +1273,7 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>10</v>
@@ -1294,10 +1288,10 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I31">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -1308,7 +1302,7 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>10</v>
@@ -1326,7 +1320,7 @@
         <v>0.59</v>
       </c>
       <c r="I32">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -1337,7 +1331,7 @@
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="1">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1352,21 +1346,21 @@
         <v>14</v>
       </c>
       <c r="H33">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="I33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
       <c r="K33">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>10</v>
@@ -1384,18 +1378,18 @@
         <v>0.53</v>
       </c>
       <c r="I34">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="1">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -1410,21 +1404,21 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I35">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="1">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -1439,21 +1433,21 @@
         <v>14</v>
       </c>
       <c r="H36">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I36">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
       </c>
       <c r="K36">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="1">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -1471,7 +1465,7 @@
         <v>0.47</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>

--- a/Impact modelling/Runs_energy_municipalities_months.xlsx
+++ b/Impact modelling/Runs_energy_municipalities_months.xlsx
@@ -471,16 +471,16 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>0.49</v>
+        <v>0.22</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
       <c r="K2">
-        <v>0.49</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -500,16 +500,16 @@
         <v>14</v>
       </c>
       <c r="H3">
-        <v>0.51</v>
+        <v>0.2</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3">
-        <v>0.46</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -529,16 +529,16 @@
         <v>14</v>
       </c>
       <c r="H4">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
       <c r="K4">
-        <v>0.47</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -558,16 +558,16 @@
         <v>14</v>
       </c>
       <c r="H5">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
       <c r="K5">
-        <v>0.44</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -587,16 +587,16 @@
         <v>14</v>
       </c>
       <c r="H6">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
       <c r="K6">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -616,16 +616,16 @@
         <v>14</v>
       </c>
       <c r="H7">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
       </c>
       <c r="K7">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -645,16 +645,16 @@
         <v>14</v>
       </c>
       <c r="H8">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
       </c>
       <c r="K8">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -674,16 +674,16 @@
         <v>14</v>
       </c>
       <c r="H9">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="I9">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
       <c r="K9">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -703,7 +703,7 @@
         <v>14</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="s">
         <v>15</v>
@@ -749,16 +749,16 @@
         <v>14</v>
       </c>
       <c r="H12">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="I12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
       </c>
       <c r="K12">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -778,16 +778,16 @@
         <v>14</v>
       </c>
       <c r="H13">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="I13">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
       <c r="K13">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -807,16 +807,16 @@
         <v>14</v>
       </c>
       <c r="H14">
-        <v>0.46</v>
+        <v>0.18</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J14" t="s">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>0.46</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -836,16 +836,16 @@
         <v>14</v>
       </c>
       <c r="H15">
-        <v>0.52</v>
+        <v>0.33</v>
       </c>
       <c r="I15">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
       <c r="K15">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -865,16 +865,16 @@
         <v>14</v>
       </c>
       <c r="H16">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
       <c r="K16">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -894,16 +894,16 @@
         <v>14</v>
       </c>
       <c r="H17">
-        <v>0.48</v>
+        <v>0.21</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
       <c r="K17">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -923,16 +923,16 @@
         <v>14</v>
       </c>
       <c r="H18">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="I18">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
       <c r="K18">
-        <v>0.49</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -952,16 +952,16 @@
         <v>14</v>
       </c>
       <c r="H19">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="I19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -981,16 +981,16 @@
         <v>14</v>
       </c>
       <c r="H20">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I20">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
       <c r="K20">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1009,11 +1009,17 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
+      <c r="H21">
+        <v>0.13</v>
+      </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
+      </c>
+      <c r="K21">
+        <v>0.08</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1033,16 +1039,16 @@
         <v>14</v>
       </c>
       <c r="H22">
-        <v>0.53</v>
+        <v>0.29</v>
       </c>
       <c r="I22">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1062,16 +1068,16 @@
         <v>14</v>
       </c>
       <c r="H23">
-        <v>0.51</v>
+        <v>0.26</v>
       </c>
       <c r="I23">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
       <c r="K23">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1091,16 +1097,16 @@
         <v>14</v>
       </c>
       <c r="H24">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="I24">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
       <c r="K24">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1120,16 +1126,16 @@
         <v>14</v>
       </c>
       <c r="H25">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="I25">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
       <c r="K25">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1149,16 +1155,16 @@
         <v>14</v>
       </c>
       <c r="H26">
-        <v>0.55</v>
+        <v>0.37</v>
       </c>
       <c r="I26">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
       <c r="K26">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1201,16 +1207,16 @@
         <v>14</v>
       </c>
       <c r="H28">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="I28">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1230,16 +1236,16 @@
         <v>14</v>
       </c>
       <c r="H29">
-        <v>0.59</v>
+        <v>0.38</v>
       </c>
       <c r="I29">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29">
-        <v>0.58</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1259,16 +1265,16 @@
         <v>14</v>
       </c>
       <c r="H30">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
       <c r="K30">
-        <v>0.63</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1288,16 +1294,16 @@
         <v>14</v>
       </c>
       <c r="H31">
-        <v>0.5600000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="I31">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1317,16 +1323,16 @@
         <v>14</v>
       </c>
       <c r="H32">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="I32">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
       <c r="K32">
-        <v>0.58</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1346,16 +1352,16 @@
         <v>14</v>
       </c>
       <c r="H33">
-        <v>0.54</v>
+        <v>0.29</v>
       </c>
       <c r="I33">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
       <c r="K33">
-        <v>0.54</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1375,16 +1381,16 @@
         <v>14</v>
       </c>
       <c r="H34">
-        <v>0.53</v>
+        <v>0.29</v>
       </c>
       <c r="I34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J34" t="s">
         <v>15</v>
       </c>
       <c r="K34">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1404,16 +1410,16 @@
         <v>14</v>
       </c>
       <c r="H35">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="I35">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
       <c r="K35">
-        <v>0.58</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1433,16 +1439,16 @@
         <v>14</v>
       </c>
       <c r="H36">
-        <v>0.5600000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I36">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
       </c>
       <c r="K36">
-        <v>0.5600000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1462,16 +1468,16 @@
         <v>14</v>
       </c>
       <c r="H37">
-        <v>0.47</v>
+        <v>0.14</v>
       </c>
       <c r="I37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
       <c r="K37">
-        <v>0.47</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
